--- a/boss_pack/priority_research_queue.xlsx
+++ b/boss_pack/priority_research_queue.xlsx
@@ -96,7 +96,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -112,6 +112,7 @@
     <col min="12" max="12" width="34" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
     <col min="14" max="14" width="42" customWidth="1"/>
+    <col min="15" max="15" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -196,6 +197,11 @@
       </c>
       <c r="N3" t="inlineStr" s="2">
         <is>
+          <t>Source Note</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr" s="2">
+        <is>
           <t>Report Href</t>
         </is>
       </c>
@@ -264,6 +270,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-airflow-air-refrigeration-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -332,6 +343,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-pat-kelly-plumbing-and-heating-contractors-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -400,6 +416,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-coen-steel-galway/ic_draft.html</t>
         </is>
       </c>
@@ -468,6 +489,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-ideal-installation-construction-galway/ic_draft.html</t>
         </is>
       </c>
@@ -536,6 +562,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-stationery-supplies-galway/ic_draft.html</t>
         </is>
       </c>
@@ -604,6 +635,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-kevin-walsh-plumbing-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -672,6 +708,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-stainless-steel-galway/ic_draft.html</t>
         </is>
       </c>
@@ -740,6 +781,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-bellville-building-construction-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -808,6 +854,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-spellman-construction-claregalway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -876,6 +927,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-primary-care-galway-city-east-health-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -944,6 +1000,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-grealish-gas-fuel-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1012,6 +1073,11 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-greaney-glass-products-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1080,6 +1146,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-claregalway-logistics-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1148,6 +1219,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-east-galway-quality-tool-hire-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1216,6 +1292,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-complete-roofing-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1284,6 +1365,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-l-zinc-roofing-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1352,6 +1438,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-tool-and-mould-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1420,6 +1511,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-o-malley-construction-claregalway-no-1-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1488,6 +1584,11 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-truck-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1556,6 +1657,11 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-iclean-professional-cleaning-services-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1624,6 +1730,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-car-care-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1692,6 +1803,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-oven-cleaning-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1760,6 +1876,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-james-cunningham-heating-contractors-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1828,6 +1949,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-maintenance-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1896,6 +2022,11 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-specsavers-hearcare-galway/ic_draft.html</t>
         </is>
       </c>
@@ -1964,6 +2095,11 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-desmond-murphy-truck-sales-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2032,6 +2168,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-j-o-toole-sons-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2100,6 +2241,11 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-healy-electrical-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2168,6 +2314,11 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-tool-mould-innovations-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2236,6 +2387,11 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-fuel-supplies-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2304,6 +2460,11 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-tuam-road-galway-service-station-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2372,6 +2533,11 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-east-galway-tyres-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2440,6 +2606,11 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-electrical-services-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2508,6 +2679,11 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-truck-and-van-testing-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2576,6 +2752,11 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-catering-galway/ic_draft.html</t>
         </is>
       </c>
@@ -2596,12 +2777,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2639,10 +2820,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/711992/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>ic_packs/cro-711992/ic_draft.html</t>
         </is>
@@ -2664,12 +2850,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2707,10 +2893,15 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/786116/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N40" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>ic_packs/cro-786116/ic_draft.html</t>
         </is>
@@ -2732,12 +2923,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2775,10 +2966,15 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/59625/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N41" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>ic_packs/cro-59625/ic_draft.html</t>
         </is>
@@ -2800,12 +2996,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2843,10 +3039,15 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/222180/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>ic_packs/cro-222180/ic_draft.html</t>
         </is>
@@ -2868,12 +3069,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2911,16 +3112,21 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/698394/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>ic_packs/cro-698394/ic_draft.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N43"/>
+  <autoFilter ref="A3:O43"/>
 </worksheet>
 </file>